--- a/Report JSS 1C.xlsx
+++ b/Report JSS 1C.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -637,9 +637,6 @@
     <t xml:space="preserve">hajjajato4@gmail.com </t>
   </si>
   <si>
-    <t xml:space="preserve">fatimamangus@gmail.com </t>
-  </si>
-  <si>
     <t xml:space="preserve">fannamursal33@gmail.com </t>
   </si>
   <si>
@@ -716,6 +713,9 @@
   </si>
   <si>
     <t>BASHIR KALLI MOHAMMED-NUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philemonnyimniba@gmail.com </t>
   </si>
 </sst>
 </file>
@@ -2014,11 +2014,41 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2035,85 +2065,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2141,6 +2094,53 @@
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3262,7 +3262,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3353,7 +3353,7 @@
         <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3449,7 +3449,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4204,7 +4204,7 @@
         <v>3442</v>
       </c>
       <c r="J2" s="171" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K2" s="135"/>
       <c r="L2" s="3"/>
@@ -4355,7 +4355,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C7" s="134" t="s">
         <v>97</v>
@@ -5036,7 +5036,7 @@
         <v>3466</v>
       </c>
       <c r="J26" s="172" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K26" s="135"/>
       <c r="L26" s="3"/>
@@ -5071,7 +5071,7 @@
         <v>3467</v>
       </c>
       <c r="J27" s="172" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K27" s="135"/>
       <c r="L27" s="3"/>
@@ -5246,7 +5246,7 @@
         <v>3472</v>
       </c>
       <c r="J32" s="172" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="K32" s="135"/>
       <c r="L32" s="3"/>
@@ -5314,7 +5314,7 @@
         <v>3474</v>
       </c>
       <c r="J34" s="172" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K34" s="135"/>
       <c r="L34" s="3"/>
@@ -5349,7 +5349,7 @@
         <v>3475</v>
       </c>
       <c r="J35" s="172" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K35" s="135"/>
       <c r="L35" s="3"/>
@@ -5384,7 +5384,7 @@
         <v>3476</v>
       </c>
       <c r="J36" s="172" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K36" s="135"/>
       <c r="L36" s="3"/>
@@ -5419,7 +5419,7 @@
         <v>3477</v>
       </c>
       <c r="J37" s="172" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K37" s="135"/>
       <c r="L37" s="3"/>
@@ -5454,7 +5454,7 @@
         <v>3478</v>
       </c>
       <c r="J38" s="172" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K38" s="135"/>
       <c r="L38" s="3"/>
@@ -5489,7 +5489,7 @@
         <v>3479</v>
       </c>
       <c r="J39" s="172" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K39" s="135"/>
       <c r="L39" s="3"/>
@@ -5524,7 +5524,7 @@
         <v>3480</v>
       </c>
       <c r="J40" s="172" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K40" s="135"/>
       <c r="L40" s="3"/>
@@ -5559,7 +5559,7 @@
         <v>3481</v>
       </c>
       <c r="J41" s="172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K41" s="135"/>
       <c r="L41" s="3"/>
@@ -8990,14 +8990,14 @@
   <sheetData>
     <row r="1" spans="1:216">
       <c r="A1" s="39"/>
-      <c r="B1" s="203" t="s">
+      <c r="B1" s="214" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
       <c r="H1" s="47"/>
       <c r="I1" s="47"/>
       <c r="J1" s="48"/>
@@ -9006,28 +9006,28 @@
       <c r="M1" s="39"/>
       <c r="N1" s="54"/>
       <c r="O1" s="53"/>
-      <c r="P1" s="208" t="s">
+      <c r="P1" s="218" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="209"/>
-      <c r="R1" s="209"/>
-      <c r="S1" s="209"/>
-      <c r="T1" s="209"/>
-      <c r="U1" s="209"/>
-      <c r="V1" s="209"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="219"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="219"/>
+      <c r="V1" s="219"/>
       <c r="W1" s="55"/>
       <c r="X1" s="55"/>
       <c r="Y1" s="52"/>
       <c r="Z1" s="77"/>
-      <c r="AA1" s="204" t="s">
+      <c r="AA1" s="208" t="s">
         <v>101</v>
       </c>
-      <c r="AB1" s="204"/>
-      <c r="AC1" s="204"/>
-      <c r="AD1" s="204"/>
-      <c r="AE1" s="204"/>
-      <c r="AF1" s="204"/>
-      <c r="AG1" s="204"/>
+      <c r="AB1" s="208"/>
+      <c r="AC1" s="208"/>
+      <c r="AD1" s="208"/>
+      <c r="AE1" s="208"/>
+      <c r="AF1" s="208"/>
+      <c r="AG1" s="208"/>
       <c r="AH1" s="77"/>
       <c r="AI1" s="77"/>
       <c r="AJ1" s="77"/>
@@ -9047,197 +9047,197 @@
       <c r="AV1" s="42"/>
       <c r="AW1" s="3"/>
       <c r="AX1" s="83"/>
-      <c r="AY1" s="205" t="s">
+      <c r="AY1" s="215" t="s">
         <v>93</v>
       </c>
-      <c r="AZ1" s="205"/>
-      <c r="BA1" s="205"/>
-      <c r="BB1" s="205"/>
-      <c r="BC1" s="205"/>
-      <c r="BD1" s="205"/>
-      <c r="BE1" s="205"/>
+      <c r="AZ1" s="215"/>
+      <c r="BA1" s="215"/>
+      <c r="BB1" s="215"/>
+      <c r="BC1" s="215"/>
+      <c r="BD1" s="215"/>
+      <c r="BE1" s="215"/>
       <c r="BF1" s="83"/>
       <c r="BG1" s="83"/>
       <c r="BH1" s="83"/>
       <c r="BI1" s="3"/>
       <c r="BJ1" s="88"/>
-      <c r="BK1" s="206" t="s">
+      <c r="BK1" s="216" t="s">
         <v>64</v>
       </c>
-      <c r="BL1" s="207"/>
-      <c r="BM1" s="207"/>
-      <c r="BN1" s="207"/>
-      <c r="BO1" s="207"/>
-      <c r="BP1" s="207"/>
-      <c r="BQ1" s="207"/>
+      <c r="BL1" s="217"/>
+      <c r="BM1" s="217"/>
+      <c r="BN1" s="217"/>
+      <c r="BO1" s="217"/>
+      <c r="BP1" s="217"/>
+      <c r="BQ1" s="217"/>
       <c r="BR1" s="88"/>
       <c r="BS1" s="88"/>
       <c r="BT1" s="88"/>
       <c r="BU1" s="3"/>
       <c r="BV1" s="93"/>
-      <c r="BW1" s="210" t="s">
+      <c r="BW1" s="209" t="s">
         <v>87</v>
       </c>
-      <c r="BX1" s="210"/>
-      <c r="BY1" s="210"/>
-      <c r="BZ1" s="210"/>
-      <c r="CA1" s="210"/>
-      <c r="CB1" s="210"/>
-      <c r="CC1" s="210"/>
+      <c r="BX1" s="209"/>
+      <c r="BY1" s="209"/>
+      <c r="BZ1" s="209"/>
+      <c r="CA1" s="209"/>
+      <c r="CB1" s="209"/>
+      <c r="CC1" s="209"/>
       <c r="CD1" s="93"/>
       <c r="CE1" s="93"/>
       <c r="CF1" s="93"/>
       <c r="CG1" s="3"/>
       <c r="CH1" s="62"/>
-      <c r="CI1" s="211" t="s">
+      <c r="CI1" s="210" t="s">
         <v>88</v>
       </c>
-      <c r="CJ1" s="211"/>
-      <c r="CK1" s="211"/>
-      <c r="CL1" s="211"/>
-      <c r="CM1" s="211"/>
-      <c r="CN1" s="211"/>
-      <c r="CO1" s="211"/>
+      <c r="CJ1" s="210"/>
+      <c r="CK1" s="210"/>
+      <c r="CL1" s="210"/>
+      <c r="CM1" s="210"/>
+      <c r="CN1" s="210"/>
+      <c r="CO1" s="210"/>
       <c r="CP1" s="62"/>
       <c r="CQ1" s="62"/>
       <c r="CR1" s="62"/>
       <c r="CS1" s="3"/>
       <c r="CT1" s="67"/>
-      <c r="CU1" s="212" t="s">
+      <c r="CU1" s="211" t="s">
         <v>67</v>
       </c>
-      <c r="CV1" s="212"/>
-      <c r="CW1" s="212"/>
-      <c r="CX1" s="212"/>
-      <c r="CY1" s="212"/>
-      <c r="CZ1" s="212"/>
-      <c r="DA1" s="212"/>
+      <c r="CV1" s="211"/>
+      <c r="CW1" s="211"/>
+      <c r="CX1" s="211"/>
+      <c r="CY1" s="211"/>
+      <c r="CZ1" s="211"/>
+      <c r="DA1" s="211"/>
       <c r="DB1" s="67"/>
       <c r="DC1" s="67"/>
       <c r="DD1" s="67"/>
       <c r="DE1" s="3"/>
       <c r="DF1" s="54"/>
-      <c r="DG1" s="213" t="s">
+      <c r="DG1" s="212" t="s">
         <v>89</v>
       </c>
-      <c r="DH1" s="213"/>
-      <c r="DI1" s="213"/>
-      <c r="DJ1" s="213"/>
-      <c r="DK1" s="213"/>
-      <c r="DL1" s="213"/>
-      <c r="DM1" s="213"/>
+      <c r="DH1" s="212"/>
+      <c r="DI1" s="212"/>
+      <c r="DJ1" s="212"/>
+      <c r="DK1" s="212"/>
+      <c r="DL1" s="212"/>
+      <c r="DM1" s="212"/>
       <c r="DN1" s="54"/>
       <c r="DO1" s="54"/>
       <c r="DP1" s="54"/>
       <c r="DQ1" s="3"/>
       <c r="DR1" s="103"/>
-      <c r="DS1" s="214" t="s">
+      <c r="DS1" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="DT1" s="214"/>
-      <c r="DU1" s="214"/>
-      <c r="DV1" s="214"/>
-      <c r="DW1" s="214"/>
-      <c r="DX1" s="214"/>
-      <c r="DY1" s="214"/>
+      <c r="DT1" s="213"/>
+      <c r="DU1" s="213"/>
+      <c r="DV1" s="213"/>
+      <c r="DW1" s="213"/>
+      <c r="DX1" s="213"/>
+      <c r="DY1" s="213"/>
       <c r="DZ1" s="103"/>
       <c r="EA1" s="103"/>
       <c r="EB1" s="103"/>
       <c r="EC1" s="3"/>
       <c r="ED1" s="72"/>
-      <c r="EE1" s="217" t="s">
+      <c r="EE1" s="205" t="s">
         <v>65</v>
       </c>
-      <c r="EF1" s="217"/>
-      <c r="EG1" s="217"/>
-      <c r="EH1" s="217"/>
-      <c r="EI1" s="217"/>
-      <c r="EJ1" s="217"/>
-      <c r="EK1" s="217"/>
+      <c r="EF1" s="205"/>
+      <c r="EG1" s="205"/>
+      <c r="EH1" s="205"/>
+      <c r="EI1" s="205"/>
+      <c r="EJ1" s="205"/>
+      <c r="EK1" s="205"/>
       <c r="EL1" s="72"/>
       <c r="EM1" s="72"/>
       <c r="EN1" s="72"/>
       <c r="EO1" s="3"/>
       <c r="EP1" s="98"/>
-      <c r="EQ1" s="218" t="s">
+      <c r="EQ1" s="206" t="s">
         <v>68</v>
       </c>
-      <c r="ER1" s="218"/>
-      <c r="ES1" s="218"/>
-      <c r="ET1" s="218"/>
-      <c r="EU1" s="218"/>
-      <c r="EV1" s="218"/>
-      <c r="EW1" s="218"/>
+      <c r="ER1" s="206"/>
+      <c r="ES1" s="206"/>
+      <c r="ET1" s="206"/>
+      <c r="EU1" s="206"/>
+      <c r="EV1" s="206"/>
+      <c r="EW1" s="206"/>
       <c r="EX1" s="98"/>
       <c r="EY1" s="98"/>
       <c r="EZ1" s="98"/>
       <c r="FA1" s="3"/>
       <c r="FB1" s="114"/>
-      <c r="FC1" s="216" t="s">
+      <c r="FC1" s="204" t="s">
         <v>66</v>
       </c>
-      <c r="FD1" s="216"/>
-      <c r="FE1" s="216"/>
-      <c r="FF1" s="216"/>
-      <c r="FG1" s="216"/>
-      <c r="FH1" s="216"/>
-      <c r="FI1" s="216"/>
+      <c r="FD1" s="204"/>
+      <c r="FE1" s="204"/>
+      <c r="FF1" s="204"/>
+      <c r="FG1" s="204"/>
+      <c r="FH1" s="204"/>
+      <c r="FI1" s="204"/>
       <c r="FJ1" s="114"/>
       <c r="FK1" s="114"/>
       <c r="FL1" s="114"/>
       <c r="FM1" s="3"/>
       <c r="FN1" s="48"/>
-      <c r="FO1" s="219" t="s">
+      <c r="FO1" s="207" t="s">
         <v>94</v>
       </c>
-      <c r="FP1" s="219"/>
-      <c r="FQ1" s="219"/>
-      <c r="FR1" s="219"/>
-      <c r="FS1" s="219"/>
-      <c r="FT1" s="219"/>
-      <c r="FU1" s="219"/>
+      <c r="FP1" s="207"/>
+      <c r="FQ1" s="207"/>
+      <c r="FR1" s="207"/>
+      <c r="FS1" s="207"/>
+      <c r="FT1" s="207"/>
+      <c r="FU1" s="207"/>
       <c r="FV1" s="48"/>
       <c r="FW1" s="48"/>
       <c r="FX1" s="48"/>
       <c r="FY1" s="3"/>
       <c r="FZ1" s="77"/>
-      <c r="GA1" s="204" t="s">
+      <c r="GA1" s="208" t="s">
         <v>95</v>
       </c>
-      <c r="GB1" s="204"/>
-      <c r="GC1" s="204"/>
-      <c r="GD1" s="204"/>
-      <c r="GE1" s="204"/>
-      <c r="GF1" s="204"/>
-      <c r="GG1" s="204"/>
+      <c r="GB1" s="208"/>
+      <c r="GC1" s="208"/>
+      <c r="GD1" s="208"/>
+      <c r="GE1" s="208"/>
+      <c r="GF1" s="208"/>
+      <c r="GG1" s="208"/>
       <c r="GH1" s="77"/>
       <c r="GI1" s="77"/>
       <c r="GJ1" s="77"/>
       <c r="GK1" s="3"/>
       <c r="GL1" s="114"/>
-      <c r="GM1" s="216" t="s">
+      <c r="GM1" s="204" t="s">
         <v>63</v>
       </c>
-      <c r="GN1" s="216"/>
-      <c r="GO1" s="216"/>
-      <c r="GP1" s="216"/>
-      <c r="GQ1" s="216"/>
-      <c r="GR1" s="216"/>
-      <c r="GS1" s="216"/>
+      <c r="GN1" s="204"/>
+      <c r="GO1" s="204"/>
+      <c r="GP1" s="204"/>
+      <c r="GQ1" s="204"/>
+      <c r="GR1" s="204"/>
+      <c r="GS1" s="204"/>
       <c r="GT1" s="114"/>
       <c r="GU1" s="114"/>
       <c r="GV1" s="114"/>
       <c r="GW1" s="3"/>
       <c r="GX1" s="108"/>
-      <c r="GY1" s="215" t="s">
+      <c r="GY1" s="203" t="s">
         <v>83</v>
       </c>
-      <c r="GZ1" s="215"/>
-      <c r="HA1" s="215"/>
-      <c r="HB1" s="215"/>
-      <c r="HC1" s="215"/>
-      <c r="HD1" s="215"/>
-      <c r="HE1" s="215"/>
+      <c r="GZ1" s="203"/>
+      <c r="HA1" s="203"/>
+      <c r="HB1" s="203"/>
+      <c r="HC1" s="203"/>
+      <c r="HD1" s="203"/>
+      <c r="HE1" s="203"/>
       <c r="HF1" s="108"/>
       <c r="HG1" s="108"/>
       <c r="HH1" s="108"/>
@@ -37169,7 +37169,7 @@
         <v>5</v>
       </c>
       <c r="HB41" s="128" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="HC41" s="108">
         <f t="shared" si="85"/>
@@ -43200,6 +43200,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AY1:BE1"/>
+    <mergeCell ref="BK1:BQ1"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="BW1:CC1"/>
+    <mergeCell ref="CI1:CO1"/>
+    <mergeCell ref="CU1:DA1"/>
+    <mergeCell ref="DG1:DM1"/>
+    <mergeCell ref="DS1:DY1"/>
     <mergeCell ref="GY1:HE1"/>
     <mergeCell ref="GM1:GS1"/>
     <mergeCell ref="EE1:EK1"/>
@@ -43207,16 +43217,6 @@
     <mergeCell ref="FC1:FI1"/>
     <mergeCell ref="FO1:FU1"/>
     <mergeCell ref="GA1:GG1"/>
-    <mergeCell ref="BW1:CC1"/>
-    <mergeCell ref="CI1:CO1"/>
-    <mergeCell ref="CU1:DA1"/>
-    <mergeCell ref="DG1:DM1"/>
-    <mergeCell ref="DS1:DY1"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AY1:BE1"/>
-    <mergeCell ref="BK1:BQ1"/>
-    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43378,114 +43378,114 @@
       <c r="A10" s="143" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="220" t="str">
+      <c r="B10" s="253" t="str">
         <f>VLOOKUP(B14,Data!A1:I51,2,0)</f>
         <v xml:space="preserve">JOHN CHINDA </v>
       </c>
-      <c r="C10" s="220"/>
-      <c r="D10" s="220"/>
-      <c r="E10" s="220"/>
-      <c r="F10" s="220"/>
-      <c r="G10" s="220"/>
+      <c r="C10" s="253"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
-      <c r="K10" s="221" t="s">
+      <c r="K10" s="258" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="221"/>
-      <c r="M10" s="220" t="str">
+      <c r="L10" s="258"/>
+      <c r="M10" s="253" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,7,0)</f>
         <v>1st</v>
       </c>
-      <c r="N10" s="222"/>
+      <c r="N10" s="257"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1">
       <c r="A11" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="223">
+      <c r="B11" s="252">
         <f>VLOOKUP(B14,Data!A2:H51,4,0)</f>
         <v>11</v>
       </c>
-      <c r="C11" s="223"/>
-      <c r="D11" s="223"/>
-      <c r="E11" s="223"/>
-      <c r="F11" s="223"/>
-      <c r="G11" s="223"/>
+      <c r="C11" s="252"/>
+      <c r="D11" s="252"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="252"/>
+      <c r="G11" s="252"/>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
-      <c r="K11" s="221" t="s">
+      <c r="K11" s="258" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="221"/>
-      <c r="M11" s="220" t="str">
+      <c r="L11" s="258"/>
+      <c r="M11" s="253" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,3,0)</f>
         <v>JSS 1 C</v>
       </c>
-      <c r="N11" s="222"/>
+      <c r="N11" s="257"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1">
       <c r="A12" s="143" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="220" t="str">
+      <c r="B12" s="253" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,5,0)</f>
         <v>GOMBE</v>
       </c>
-      <c r="C12" s="220"/>
-      <c r="D12" s="220"/>
-      <c r="E12" s="220"/>
-      <c r="F12" s="220"/>
-      <c r="G12" s="220"/>
+      <c r="C12" s="253"/>
+      <c r="D12" s="253"/>
+      <c r="E12" s="253"/>
+      <c r="F12" s="253"/>
+      <c r="G12" s="253"/>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
-      <c r="K12" s="221" t="s">
+      <c r="K12" s="258" t="s">
         <v>42</v>
       </c>
-      <c r="L12" s="221"/>
-      <c r="M12" s="220" t="str">
+      <c r="L12" s="258"/>
+      <c r="M12" s="253" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,8,0)</f>
         <v>16th January, 2026</v>
       </c>
-      <c r="N12" s="222"/>
+      <c r="N12" s="257"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1">
       <c r="A13" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="220" t="str">
+      <c r="B13" s="253" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,6,0)</f>
         <v>GUGUWA</v>
       </c>
-      <c r="C13" s="220"/>
-      <c r="D13" s="220"/>
-      <c r="E13" s="220"/>
-      <c r="F13" s="220"/>
-      <c r="G13" s="220"/>
+      <c r="C13" s="253"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
+      <c r="F13" s="253"/>
+      <c r="G13" s="253"/>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
-      <c r="K13" s="221" t="s">
+      <c r="K13" s="258" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="221"/>
-      <c r="M13" s="220" t="str">
+      <c r="L13" s="258"/>
+      <c r="M13" s="253" t="str">
         <f>IF(M20&gt;=40,"Passed","Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="N13" s="222"/>
+      <c r="N13" s="257"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1">
       <c r="A14" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="223">
+      <c r="B14" s="252">
         <v>40</v>
       </c>
-      <c r="C14" s="223"/>
+      <c r="C14" s="252"/>
       <c r="D14" s="140"/>
       <c r="E14" s="140"/>
       <c r="F14" s="140"/>
@@ -43493,10 +43493,10 @@
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
-      <c r="K14" s="220"/>
-      <c r="L14" s="220"/>
-      <c r="M14" s="224"/>
-      <c r="N14" s="225"/>
+      <c r="K14" s="253"/>
+      <c r="L14" s="253"/>
+      <c r="M14" s="254"/>
+      <c r="N14" s="255"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1">
       <c r="A15" s="143" t="s">
@@ -43514,10 +43514,10 @@
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
-      <c r="K15" s="226"/>
-      <c r="L15" s="226"/>
-      <c r="M15" s="220"/>
-      <c r="N15" s="222"/>
+      <c r="K15" s="256"/>
+      <c r="L15" s="256"/>
+      <c r="M15" s="253"/>
+      <c r="N15" s="257"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1">
       <c r="A16" s="143" t="s">
@@ -43557,111 +43557,111 @@
       <c r="N17" s="15"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1">
-      <c r="A18" s="250" t="s">
+      <c r="A18" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="252" t="s">
+      <c r="B18" s="225" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="252" t="s">
+      <c r="D18" s="225" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="252" t="s">
+      <c r="E18" s="225" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="254" t="s">
+      <c r="F18" s="227" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="252" t="s">
+      <c r="G18" s="225" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="252" t="s">
+      <c r="H18" s="225" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="254" t="s">
+      <c r="I18" s="227" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="256" t="s">
+      <c r="J18" s="229" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="227" t="s">
+      <c r="K18" s="244" t="s">
         <v>54</v>
       </c>
-      <c r="L18" s="228"/>
-      <c r="M18" s="229">
+      <c r="L18" s="245"/>
+      <c r="M18" s="246">
         <f>100*(COUNTIF(H23:H40,"&gt;5"))</f>
         <v>1700</v>
       </c>
-      <c r="N18" s="230"/>
+      <c r="N18" s="247"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1">
-      <c r="A19" s="251"/>
-      <c r="B19" s="253"/>
-      <c r="C19" s="253"/>
-      <c r="D19" s="253"/>
-      <c r="E19" s="253"/>
-      <c r="F19" s="255"/>
-      <c r="G19" s="253"/>
-      <c r="H19" s="253"/>
-      <c r="I19" s="255"/>
-      <c r="J19" s="257"/>
-      <c r="K19" s="231" t="s">
+      <c r="A19" s="224"/>
+      <c r="B19" s="226"/>
+      <c r="C19" s="226"/>
+      <c r="D19" s="226"/>
+      <c r="E19" s="226"/>
+      <c r="F19" s="228"/>
+      <c r="G19" s="226"/>
+      <c r="H19" s="226"/>
+      <c r="I19" s="228"/>
+      <c r="J19" s="230"/>
+      <c r="K19" s="248" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="232"/>
-      <c r="M19" s="233">
+      <c r="L19" s="249"/>
+      <c r="M19" s="236">
         <f>SUM(H23:H40)</f>
         <v>728</v>
       </c>
-      <c r="N19" s="234"/>
+      <c r="N19" s="237"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1">
-      <c r="A20" s="251"/>
-      <c r="B20" s="253"/>
-      <c r="C20" s="253"/>
-      <c r="D20" s="253"/>
-      <c r="E20" s="253"/>
-      <c r="F20" s="255"/>
-      <c r="G20" s="253"/>
-      <c r="H20" s="253"/>
-      <c r="I20" s="255"/>
-      <c r="J20" s="257"/>
-      <c r="K20" s="231" t="s">
+      <c r="A20" s="224"/>
+      <c r="B20" s="226"/>
+      <c r="C20" s="226"/>
+      <c r="D20" s="226"/>
+      <c r="E20" s="226"/>
+      <c r="F20" s="228"/>
+      <c r="G20" s="226"/>
+      <c r="H20" s="226"/>
+      <c r="I20" s="228"/>
+      <c r="J20" s="230"/>
+      <c r="K20" s="248" t="s">
         <v>56</v>
       </c>
-      <c r="L20" s="232"/>
-      <c r="M20" s="235">
+      <c r="L20" s="249"/>
+      <c r="M20" s="250">
         <f>VLOOKUP(B14,Bsheet!A2:V51,21,0)</f>
         <v>42.764705882352942</v>
       </c>
-      <c r="N20" s="236"/>
+      <c r="N20" s="251"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1">
-      <c r="A21" s="251"/>
-      <c r="B21" s="253"/>
-      <c r="C21" s="253"/>
-      <c r="D21" s="253"/>
-      <c r="E21" s="253"/>
-      <c r="F21" s="255"/>
-      <c r="G21" s="253"/>
-      <c r="H21" s="253"/>
-      <c r="I21" s="255"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="237" t="s">
+      <c r="A21" s="224"/>
+      <c r="B21" s="226"/>
+      <c r="C21" s="226"/>
+      <c r="D21" s="226"/>
+      <c r="E21" s="226"/>
+      <c r="F21" s="228"/>
+      <c r="G21" s="226"/>
+      <c r="H21" s="226"/>
+      <c r="I21" s="228"/>
+      <c r="J21" s="231"/>
+      <c r="K21" s="238" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="238"/>
-      <c r="M21" s="239">
+      <c r="L21" s="239"/>
+      <c r="M21" s="240">
         <f>VLOOKUP(B14,Bsheet!A2:V51,22,0)</f>
         <v>29</v>
       </c>
-      <c r="N21" s="240"/>
+      <c r="N21" s="241"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1">
-      <c r="A22" s="251"/>
+      <c r="A22" s="224"/>
       <c r="B22" s="28" t="s">
         <v>58</v>
       </c>
@@ -43685,12 +43685,12 @@
       </c>
       <c r="I22" s="122"/>
       <c r="J22" s="123"/>
-      <c r="K22" s="241" t="s">
+      <c r="K22" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="241"/>
-      <c r="M22" s="241"/>
-      <c r="N22" s="242"/>
+      <c r="L22" s="242"/>
+      <c r="M22" s="242"/>
+      <c r="N22" s="243"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1">
       <c r="A23" s="29" t="s">
@@ -43732,13 +43732,13 @@
         <f>VLOOKUP(B14,Scoresheet!A3:K52,11,0)</f>
         <v>P</v>
       </c>
-      <c r="K23" s="243" t="str">
+      <c r="K23" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,12,0)</f>
         <v>Pass</v>
       </c>
-      <c r="L23" s="233"/>
-      <c r="M23" s="233"/>
-      <c r="N23" s="234"/>
+      <c r="L23" s="236"/>
+      <c r="M23" s="236"/>
+      <c r="N23" s="237"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1">
       <c r="A24" s="29" t="s">
@@ -43780,13 +43780,13 @@
         <f>VLOOKUP(B14,Scoresheet!M3:W52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K24" s="243" t="str">
+      <c r="K24" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!M3:X52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L24" s="233"/>
-      <c r="M24" s="233"/>
-      <c r="N24" s="234"/>
+      <c r="L24" s="236"/>
+      <c r="M24" s="236"/>
+      <c r="N24" s="237"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1">
       <c r="A25" s="29" t="s">
@@ -43828,13 +43828,13 @@
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K25" s="243" t="str">
+      <c r="K25" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!Y3:AJ52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L25" s="233"/>
-      <c r="M25" s="233"/>
-      <c r="N25" s="234"/>
+      <c r="L25" s="236"/>
+      <c r="M25" s="236"/>
+      <c r="N25" s="237"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1">
       <c r="A26" s="29" t="s">
@@ -43876,13 +43876,13 @@
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K26" s="243" t="str">
+      <c r="K26" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!AK3:AV52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L26" s="233"/>
-      <c r="M26" s="233"/>
-      <c r="N26" s="234"/>
+      <c r="L26" s="236"/>
+      <c r="M26" s="236"/>
+      <c r="N26" s="237"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1">
       <c r="A27" s="29" t="s">
@@ -43924,13 +43924,13 @@
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K27" s="243" t="str">
+      <c r="K27" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!AW3:BH52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L27" s="233"/>
-      <c r="M27" s="233"/>
-      <c r="N27" s="234"/>
+      <c r="L27" s="236"/>
+      <c r="M27" s="236"/>
+      <c r="N27" s="237"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1">
       <c r="A28" s="29" t="s">
@@ -43972,13 +43972,13 @@
         <f>VLOOKUP(B14,Scoresheet!BI3:BU52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K28" s="243" t="str">
+      <c r="K28" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!BI3:BT52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L28" s="233"/>
-      <c r="M28" s="233"/>
-      <c r="N28" s="234"/>
+      <c r="L28" s="236"/>
+      <c r="M28" s="236"/>
+      <c r="N28" s="237"/>
     </row>
     <row r="29" spans="1:14" ht="18" customHeight="1">
       <c r="A29" s="29" t="s">
@@ -44020,13 +44020,13 @@
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K29" s="243" t="str">
+      <c r="K29" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!BU3:CF52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L29" s="233"/>
-      <c r="M29" s="233"/>
-      <c r="N29" s="234"/>
+      <c r="L29" s="236"/>
+      <c r="M29" s="236"/>
+      <c r="N29" s="237"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1">
       <c r="A30" s="29" t="s">
@@ -44068,13 +44068,13 @@
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K30" s="243" t="str">
+      <c r="K30" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!CG3:CR52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L30" s="233"/>
-      <c r="M30" s="233"/>
-      <c r="N30" s="234"/>
+      <c r="L30" s="236"/>
+      <c r="M30" s="236"/>
+      <c r="N30" s="237"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1">
       <c r="A31" s="29" t="s">
@@ -44116,13 +44116,13 @@
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,11,0)</f>
         <v>P</v>
       </c>
-      <c r="K31" s="243" t="str">
+      <c r="K31" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!CS3:DD52,12,0)</f>
         <v>Pass</v>
       </c>
-      <c r="L31" s="233"/>
-      <c r="M31" s="233"/>
-      <c r="N31" s="234"/>
+      <c r="L31" s="236"/>
+      <c r="M31" s="236"/>
+      <c r="N31" s="237"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1">
       <c r="A32" s="29" t="s">
@@ -44164,13 +44164,13 @@
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K32" s="243" t="str">
+      <c r="K32" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!DE3:DP52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L32" s="233"/>
-      <c r="M32" s="233"/>
-      <c r="N32" s="234"/>
+      <c r="L32" s="236"/>
+      <c r="M32" s="236"/>
+      <c r="N32" s="237"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1">
       <c r="A33" s="29" t="s">
@@ -44212,13 +44212,13 @@
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K33" s="243" t="str">
+      <c r="K33" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EB52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L33" s="233"/>
-      <c r="M33" s="233"/>
-      <c r="N33" s="234"/>
+      <c r="L33" s="236"/>
+      <c r="M33" s="236"/>
+      <c r="N33" s="237"/>
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1">
       <c r="A34" s="29" t="s">
@@ -44260,13 +44260,13 @@
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K34" s="243" t="str">
+      <c r="K34" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!EC3:EN52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L34" s="233"/>
-      <c r="M34" s="233"/>
-      <c r="N34" s="234"/>
+      <c r="L34" s="236"/>
+      <c r="M34" s="236"/>
+      <c r="N34" s="237"/>
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1">
       <c r="A35" s="29" t="s">
@@ -44308,13 +44308,13 @@
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K35" s="243" t="str">
+      <c r="K35" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO3:EZ52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L35" s="233"/>
-      <c r="M35" s="233"/>
-      <c r="N35" s="234"/>
+      <c r="L35" s="236"/>
+      <c r="M35" s="236"/>
+      <c r="N35" s="237"/>
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1">
       <c r="A36" s="29" t="s">
@@ -44356,13 +44356,13 @@
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K36" s="243" t="str">
+      <c r="K36" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!FA3:FL52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L36" s="233"/>
-      <c r="M36" s="233"/>
-      <c r="N36" s="234"/>
+      <c r="L36" s="236"/>
+      <c r="M36" s="236"/>
+      <c r="N36" s="237"/>
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1">
       <c r="A37" s="29" t="s">
@@ -44404,13 +44404,13 @@
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K37" s="243" t="str">
+      <c r="K37" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!FM3:FX52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L37" s="233"/>
-      <c r="M37" s="233"/>
-      <c r="N37" s="234"/>
+      <c r="L37" s="236"/>
+      <c r="M37" s="236"/>
+      <c r="N37" s="237"/>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1">
       <c r="A38" s="29" t="s">
@@ -44452,13 +44452,13 @@
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K38" s="243" t="str">
+      <c r="K38" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!FY3:GJ52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L38" s="233"/>
-      <c r="M38" s="233"/>
-      <c r="N38" s="234"/>
+      <c r="L38" s="236"/>
+      <c r="M38" s="236"/>
+      <c r="N38" s="237"/>
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1">
       <c r="A39" s="29" t="s">
@@ -44500,13 +44500,13 @@
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,11,0)</f>
         <v>P</v>
       </c>
-      <c r="K39" s="243" t="str">
+      <c r="K39" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!GK3:GW52,12,0)</f>
         <v>Pass</v>
       </c>
-      <c r="L39" s="233"/>
-      <c r="M39" s="233"/>
-      <c r="N39" s="234"/>
+      <c r="L39" s="236"/>
+      <c r="M39" s="236"/>
+      <c r="N39" s="237"/>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
       <c r="A40" s="29" t="s">
@@ -44548,13 +44548,13 @@
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,11,0)</f>
         <v/>
       </c>
-      <c r="K40" s="243" t="str">
+      <c r="K40" s="235" t="str">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,12,0)</f>
         <v/>
       </c>
-      <c r="L40" s="233"/>
-      <c r="M40" s="233"/>
-      <c r="N40" s="234"/>
+      <c r="L40" s="236"/>
+      <c r="M40" s="236"/>
+      <c r="N40" s="237"/>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
       <c r="A41" s="22"/>
@@ -44578,20 +44578,20 @@
       </c>
       <c r="B42" s="34"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="244" t="s">
+      <c r="D42" s="233" t="s">
         <v>71</v>
       </c>
-      <c r="E42" s="244"/>
+      <c r="E42" s="233"/>
       <c r="F42" s="36"/>
       <c r="G42" s="37"/>
-      <c r="H42" s="245" t="s">
+      <c r="H42" s="234" t="s">
         <v>72</v>
       </c>
-      <c r="I42" s="245"/>
-      <c r="J42" s="245"/>
-      <c r="K42" s="245"/>
-      <c r="L42" s="245"/>
-      <c r="M42" s="245"/>
+      <c r="I42" s="234"/>
+      <c r="J42" s="234"/>
+      <c r="K42" s="234"/>
+      <c r="L42" s="234"/>
+      <c r="M42" s="234"/>
       <c r="N42" s="38"/>
       <c r="O42" s="17"/>
     </row>
@@ -44604,23 +44604,23 @@
         <v>5</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="244" t="s">
+      <c r="D43" s="233" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="244"/>
+      <c r="E43" s="233"/>
       <c r="F43" s="36">
         <f>VLOOKUP(B14,Skills!A2:H51,3,0)</f>
         <v>3</v>
       </c>
       <c r="G43" s="37"/>
-      <c r="H43" s="245" t="s">
+      <c r="H43" s="234" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="245"/>
-      <c r="J43" s="245"/>
-      <c r="K43" s="245"/>
-      <c r="L43" s="245"/>
-      <c r="M43" s="245"/>
+      <c r="I43" s="234"/>
+      <c r="J43" s="234"/>
+      <c r="K43" s="234"/>
+      <c r="L43" s="234"/>
+      <c r="M43" s="234"/>
       <c r="N43" s="38"/>
       <c r="O43" s="17"/>
     </row>
@@ -44633,23 +44633,23 @@
         <v>3</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="244" t="s">
+      <c r="D44" s="233" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="244"/>
+      <c r="E44" s="233"/>
       <c r="F44" s="36">
         <f>VLOOKUP(B14,Skills!A2:H51,4,0)</f>
         <v>3</v>
       </c>
       <c r="G44" s="37"/>
-      <c r="H44" s="245" t="s">
+      <c r="H44" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="I44" s="245"/>
-      <c r="J44" s="245"/>
-      <c r="K44" s="245"/>
-      <c r="L44" s="245"/>
-      <c r="M44" s="245"/>
+      <c r="I44" s="234"/>
+      <c r="J44" s="234"/>
+      <c r="K44" s="234"/>
+      <c r="L44" s="234"/>
+      <c r="M44" s="234"/>
       <c r="N44" s="38"/>
       <c r="O44" s="17"/>
     </row>
@@ -44662,23 +44662,23 @@
         <v>3</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="244" t="s">
+      <c r="D45" s="233" t="s">
         <v>32</v>
       </c>
-      <c r="E45" s="244"/>
+      <c r="E45" s="233"/>
       <c r="F45" s="36">
         <f>VLOOKUP(B14,Skills!A2:H51,5,0)</f>
         <v>5</v>
       </c>
       <c r="G45" s="37"/>
-      <c r="H45" s="245" t="s">
+      <c r="H45" s="234" t="s">
         <v>75</v>
       </c>
-      <c r="I45" s="245"/>
-      <c r="J45" s="245"/>
-      <c r="K45" s="245"/>
-      <c r="L45" s="245"/>
-      <c r="M45" s="245"/>
+      <c r="I45" s="234"/>
+      <c r="J45" s="234"/>
+      <c r="K45" s="234"/>
+      <c r="L45" s="234"/>
+      <c r="M45" s="234"/>
       <c r="N45" s="38"/>
       <c r="O45" s="17"/>
     </row>
@@ -44691,23 +44691,23 @@
         <v>2</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="244" t="s">
+      <c r="D46" s="233" t="s">
         <v>33</v>
       </c>
-      <c r="E46" s="244"/>
+      <c r="E46" s="233"/>
       <c r="F46" s="36">
         <f>VLOOKUP(B14,Skills!A2:H51,6,0)</f>
         <v>3</v>
       </c>
       <c r="G46" s="37"/>
-      <c r="H46" s="245" t="s">
+      <c r="H46" s="234" t="s">
         <v>76</v>
       </c>
-      <c r="I46" s="245"/>
-      <c r="J46" s="245"/>
-      <c r="K46" s="245"/>
-      <c r="L46" s="245"/>
-      <c r="M46" s="245"/>
+      <c r="I46" s="234"/>
+      <c r="J46" s="234"/>
+      <c r="K46" s="234"/>
+      <c r="L46" s="234"/>
+      <c r="M46" s="234"/>
       <c r="N46" s="38"/>
       <c r="O46" s="17"/>
     </row>
@@ -44720,23 +44720,23 @@
         <v>4</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="244" t="s">
+      <c r="D47" s="233" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="244"/>
+      <c r="E47" s="233"/>
       <c r="F47" s="36">
         <f>VLOOKUP(B16,Skills!A2:H51,7,0)</f>
         <v>0</v>
       </c>
       <c r="G47" s="37"/>
-      <c r="H47" s="245" t="s">
+      <c r="H47" s="234" t="s">
         <v>77</v>
       </c>
-      <c r="I47" s="245"/>
-      <c r="J47" s="245"/>
-      <c r="K47" s="245"/>
-      <c r="L47" s="245"/>
-      <c r="M47" s="245"/>
+      <c r="I47" s="234"/>
+      <c r="J47" s="234"/>
+      <c r="K47" s="234"/>
+      <c r="L47" s="234"/>
+      <c r="M47" s="234"/>
       <c r="N47" s="38"/>
       <c r="O47" s="17"/>
     </row>
@@ -44841,11 +44841,11 @@
       <c r="O52" s="17"/>
     </row>
     <row r="53" spans="1:20" ht="18" customHeight="1">
-      <c r="A53" s="246" t="s">
+      <c r="A53" s="220" t="s">
         <v>78</v>
       </c>
-      <c r="B53" s="247"/>
-      <c r="C53" s="247"/>
+      <c r="B53" s="221"/>
+      <c r="C53" s="221"/>
       <c r="D53" s="17" t="s">
         <v>79</v>
       </c>
@@ -44863,16 +44863,16 @@
       <c r="M53" s="17"/>
       <c r="N53" s="16"/>
       <c r="O53" s="17"/>
-      <c r="R53" s="249"/>
-      <c r="S53" s="249"/>
-      <c r="T53" s="249"/>
+      <c r="R53" s="222"/>
+      <c r="S53" s="222"/>
+      <c r="T53" s="222"/>
     </row>
     <row r="54" spans="1:20" ht="18" customHeight="1">
-      <c r="A54" s="246" t="s">
+      <c r="A54" s="220" t="s">
         <v>80</v>
       </c>
-      <c r="B54" s="247"/>
-      <c r="C54" s="247"/>
+      <c r="B54" s="221"/>
+      <c r="C54" s="221"/>
       <c r="D54" s="17" t="s">
         <v>79</v>
       </c>
@@ -44887,43 +44887,43 @@
       <c r="M54" s="17"/>
       <c r="N54" s="16"/>
       <c r="O54" s="17"/>
-      <c r="R54" s="249"/>
-      <c r="S54" s="249"/>
-      <c r="T54" s="249"/>
+      <c r="R54" s="222"/>
+      <c r="S54" s="222"/>
+      <c r="T54" s="222"/>
     </row>
     <row r="55" spans="1:20" ht="18" customHeight="1">
-      <c r="A55" s="246" t="s">
+      <c r="A55" s="220" t="s">
         <v>81</v>
       </c>
-      <c r="B55" s="247"/>
-      <c r="C55" s="247"/>
+      <c r="B55" s="221"/>
+      <c r="C55" s="221"/>
       <c r="D55" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="248" t="str">
+      <c r="E55" s="232" t="str">
         <f>VLOOKUP(B14,Comments!A2:C51,3,0)</f>
         <v>Nil</v>
       </c>
-      <c r="F55" s="248"/>
-      <c r="G55" s="248"/>
-      <c r="H55" s="248"/>
-      <c r="I55" s="248"/>
-      <c r="J55" s="248"/>
+      <c r="F55" s="232"/>
+      <c r="G55" s="232"/>
+      <c r="H55" s="232"/>
+      <c r="I55" s="232"/>
+      <c r="J55" s="232"/>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" s="16"/>
       <c r="O55" s="17"/>
-      <c r="R55" s="249"/>
-      <c r="S55" s="249"/>
-      <c r="T55" s="249"/>
+      <c r="R55" s="222"/>
+      <c r="S55" s="222"/>
+      <c r="T55" s="222"/>
     </row>
     <row r="56" spans="1:20" ht="18" customHeight="1">
-      <c r="A56" s="246" t="s">
+      <c r="A56" s="220" t="s">
         <v>82</v>
       </c>
-      <c r="B56" s="247"/>
-      <c r="C56" s="247"/>
+      <c r="B56" s="221"/>
+      <c r="C56" s="221"/>
       <c r="D56" s="17" t="s">
         <v>79</v>
       </c>
@@ -44941,9 +44941,9 @@
       <c r="M56" s="17"/>
       <c r="N56" s="16"/>
       <c r="O56" s="17"/>
-      <c r="R56" s="249"/>
-      <c r="S56" s="249"/>
-      <c r="T56" s="249"/>
+      <c r="R56" s="222"/>
+      <c r="S56" s="222"/>
+      <c r="T56" s="222"/>
     </row>
     <row r="57" spans="1:20" ht="18" customHeight="1" thickBot="1">
       <c r="A57" s="24"/>
@@ -44980,6 +44980,65 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="75">
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="H47:M47"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="R56:T56"/>
     <mergeCell ref="A18:A22"/>
@@ -44996,65 +45055,6 @@
     <mergeCell ref="R53:T53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="R54:T54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="K36:N36"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.25" bottom="0" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
@@ -45090,7 +45090,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="13" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="262" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B1" s="263"/>
       <c r="C1" s="263"/>
@@ -45122,10 +45122,10 @@
     </row>
     <row r="3" spans="1:12" ht="15.75">
       <c r="A3" s="190" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" s="265" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C3" s="265"/>
       <c r="D3" s="265"/>
@@ -45140,7 +45140,7 @@
     </row>
     <row r="4" spans="1:12" ht="15.75">
       <c r="A4" s="259" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B4" s="260"/>
       <c r="C4" s="260"/>
@@ -45156,31 +45156,31 @@
     </row>
     <row r="5" spans="1:12" ht="105">
       <c r="A5" s="191" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="192" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="C5" s="193" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="193" t="s">
+      <c r="D5" s="193" t="s">
         <v>220</v>
       </c>
-      <c r="D5" s="193" t="s">
+      <c r="E5" s="193" t="s">
         <v>221</v>
       </c>
-      <c r="E5" s="193" t="s">
+      <c r="F5" s="193" t="s">
         <v>222</v>
       </c>
-      <c r="F5" s="193" t="s">
+      <c r="G5" s="193" t="s">
         <v>223</v>
       </c>
-      <c r="G5" s="193" t="s">
+      <c r="H5" s="193" t="s">
         <v>224</v>
       </c>
-      <c r="H5" s="193" t="s">
+      <c r="I5" s="193" t="s">
         <v>225</v>
-      </c>
-      <c r="I5" s="193" t="s">
-        <v>226</v>
       </c>
       <c r="J5" s="193" t="s">
         <v>16</v>
@@ -45345,7 +45345,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C11" s="196"/>
       <c r="D11" s="196"/>
